--- a/ai4sh/import_data/utility/observation/excel/unit.xlsx
+++ b/ai4sh/import_data/utility/observation/excel/unit.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="241">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -731,6 +731,18 @@
   </si>
   <si>
     <t xml:space="preserve">μS*cm^-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nominal class/category</t>
   </si>
 </sst>
 </file>
@@ -923,37 +935,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1026,8 +1038,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E75"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="32.85"/>
@@ -2289,6 +2301,23 @@
       </c>
       <c r="E74" s="1" t="s">
         <v>203</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
